--- a/test/fixtures/JinSheet-Sample.xlsx
+++ b/test/fixtures/JinSheet-Sample.xlsx
@@ -9,6 +9,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <cols>
+    <col min="1" max="1" width="6.14" customWidth="1"/>
+    <col min="2" max="2" width="6.14" customWidth="1"/>
+    <col min="3" max="3" width="6.14" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
